--- a/JsonConverter/ExcelFiles/Trap.xlsx
+++ b/JsonConverter/ExcelFiles/Trap.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t xml:space="preserve">함정 ID</t>
   </si>
@@ -40,6 +40,9 @@
     <t xml:space="preserve">string</t>
   </si>
   <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
     <t xml:space="preserve">Id</t>
   </si>
   <si>
@@ -47,6 +50,9 @@
   </si>
   <si>
     <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damage</t>
   </si>
   <si>
     <t xml:space="preserve">trap_solid_spike_01</t>
@@ -512,33 +518,37 @@
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
     <row r="3" s="6" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>10</v>

--- a/JsonConverter/ExcelFiles/Trap.xlsx
+++ b/JsonConverter/ExcelFiles/Trap.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t xml:space="preserve">함정 ID</t>
   </si>
@@ -55,6 +55,9 @@
     <t xml:space="preserve">Damage</t>
   </si>
   <si>
+    <t xml:space="preserve">PrefabPath</t>
+  </si>
+  <si>
     <t xml:space="preserve">trap_solid_spike_01</t>
   </si>
   <si>
@@ -62,6 +65,9 @@
   </si>
   <si>
     <t xml:space="preserve">일반적인 가시 함정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prefab/Obj/Trap/Trap_Spike</t>
   </si>
 </sst>
 </file>
@@ -537,23 +543,27 @@
       <c r="D3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="F3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="F4" s="2"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>

--- a/JsonConverter/ExcelFiles/Trap.xlsx
+++ b/JsonConverter/ExcelFiles/Trap.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t xml:space="preserve">함정 ID</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t xml:space="preserve">데미지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">프리펩 경로 (=어드레서블 네임)</t>
   </si>
   <si>
     <t xml:space="preserve">(name)</t>
@@ -67,7 +70,7 @@
     <t xml:space="preserve">일반적인 가시 함정</t>
   </si>
   <si>
-    <t xml:space="preserve">Prefab/Obj/Trap/Trap_Spike</t>
+    <t xml:space="preserve">Trap/Trap_Spike</t>
   </si>
 </sst>
 </file>
@@ -77,7 +80,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -116,6 +119,13 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -200,7 +210,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -217,7 +227,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -229,11 +243,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -512,361 +526,363 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3"/>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" s="6" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="3" s="7" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="5"/>
+      <c r="E3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>15</v>
+      <c r="E4" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="F4" s="2"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="E25" s="7"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="E25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="E26" s="7"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="E26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="E27" s="7"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="E27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="E28" s="7"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="E28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
